--- a/modeles/xlsx/SORTIE_SOP.xlsx
+++ b/modeles/xlsx/SORTIE_SOP.xlsx
@@ -476,12 +476,13 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="21" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,40 +508,45 @@
       </c>
       <c r="E1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Scenario</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Libelle</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Statut</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Date reunion S&amp;OP</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Version coefficients</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
+      <c r="J1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Cree par</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr" s="1">
+      <c r="K1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Cree le</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr" s="1">
+      <c r="L1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Verrouillee</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr" s="1">
+      <c r="M1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Commentaire</t>
         </is>
@@ -560,17 +566,18 @@
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="31" customWidth="1"/>
     <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
-    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="17" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="17" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -611,55 +618,60 @@
       </c>
       <c r="H1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Tendance retenue</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Qte TC</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
+      <c r="J1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Qte evenements</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr" s="1">
+      <c r="K1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Qte correction</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr" s="1">
+      <c r="L1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Qte arbitree</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr" s="1">
+      <c r="M1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Qte validee</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr" s="1">
+      <c r="N1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Unite stock</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr" s="1">
+      <c r="O1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Poids article</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr" s="1">
+      <c r="P1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Statut</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr" s="1">
+      <c r="Q1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Version</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr" s="1">
+      <c r="R1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Modifie par</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr" s="1">
+      <c r="S1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Modifie le</t>
         </is>
@@ -907,12 +919,11 @@
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
-    <col min="6" max="6" width="21" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="19" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -923,45 +934,40 @@
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Scenario</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Semaine</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr" s="1">
+      <c r="D1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Plateforme</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Marche</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Stock debut T</t>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Code produit</t>
         </is>
       </c>
       <c r="F1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Sorties prevues T</t>
+          <t xml:space="preserve">Mouvement</t>
         </is>
       </c>
       <c r="G1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Entrees fournisseurs T</t>
+          <t xml:space="preserve">Quantite</t>
         </is>
       </c>
       <c r="H1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Stock fin T</t>
+          <t xml:space="preserve">Origine</t>
         </is>
       </c>
       <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Couverture mois</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Alerte</t>
         </is>

--- a/modeles/xlsx/SORTIE_SOP.xlsx
+++ b/modeles/xlsx/SORTIE_SOP.xlsx
@@ -10,13 +10,14 @@
     <sheet name="EVENEMENTS_COMMERCE" sheetId="6" r:id="rId6"/>
     <sheet name="STOCKS_PROJETES" sheetId="7" r:id="rId7"/>
     <sheet name="FIABILITE" sheetId="8" r:id="rId8"/>
-    <sheet name="ALERTES" sheetId="9" r:id="rId9"/>
-    <sheet name="DECISIONS" sheetId="10" r:id="rId10"/>
-    <sheet name="JOURNAL" sheetId="11" r:id="rId11"/>
-    <sheet name="OPERATIONS" sheetId="12" r:id="rId12"/>
-    <sheet name="CONTRAT" sheetId="13" r:id="rId13"/>
-    <sheet name="PUBLICATION_MENSUELLE" sheetId="14" r:id="rId14"/>
-    <sheet name="PUBLICATION_HEBDO" sheetId="15" r:id="rId15"/>
+    <sheet name="RUPTURES" sheetId="9" r:id="rId9"/>
+    <sheet name="ALERTES" sheetId="10" r:id="rId10"/>
+    <sheet name="DECISIONS" sheetId="11" r:id="rId11"/>
+    <sheet name="JOURNAL" sheetId="12" r:id="rId12"/>
+    <sheet name="OPERATIONS" sheetId="13" r:id="rId13"/>
+    <sheet name="CONTRAT" sheetId="14" r:id="rId14"/>
+    <sheet name="PUBLICATION_MENSUELLE" sheetId="15" r:id="rId15"/>
+    <sheet name="PUBLICATION_HEBDO" sheetId="16" r:id="rId16"/>
   </sheets>
 </workbook>
 </file>
@@ -122,6 +123,71 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID alerte</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Code alerte</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Cle</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Valeur</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Seuil</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Statut</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Acquittee par</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Acquittee le</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
@@ -172,7 +238,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -231,7 +297,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -272,7 +338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -313,20 +379,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -347,63 +416,81 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Scenario</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Date validation</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Code produit</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Entite</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Plateforme</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Mois</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Quantite</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Quantite demande</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Quantite reelle</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Unite stock</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tonnes</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Tonnes demande</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Tonnes reelle</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
-    <col min="10" max="10" width="15" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="19" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
+    <col min="14" max="14" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -424,42 +511,57 @@
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Scenario</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Date validation</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Code produit</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Entite</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Plateforme</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Semaine</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Quantite</t>
-        </is>
-      </c>
       <c r="J1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Quantite demande</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Quantite reelle</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Unite stock</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Tonnes</t>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Tonnes demande</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Tonnes reelle</t>
         </is>
       </c>
     </row>
@@ -572,12 +674,13 @@
     <col min="11" max="11" width="18" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="15" customWidth="1"/>
-    <col min="14" max="14" width="15" customWidth="1"/>
-    <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="14" max="14" width="23" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
+    <col min="16" max="16" width="17" customWidth="1"/>
     <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="15" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="15" customWidth="1"/>
+    <col min="20" max="20" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,30 +751,35 @@
       </c>
       <c r="N1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Qte reelle attendue</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Unite stock</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr" s="1">
+      <c r="P1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Poids article</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr" s="1">
+      <c r="Q1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Statut</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr" s="1">
+      <c r="R1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Version</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr" s="1">
+      <c r="S1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Modifie par</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr" s="1">
+      <c r="T1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Modifie le</t>
         </is>
@@ -722,13 +830,14 @@
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="15" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
     <col min="14" max="14" width="14" customWidth="1"/>
     <col min="15" max="15" width="14" customWidth="1"/>
     <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -779,35 +888,40 @@
       </c>
       <c r="J1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Methode estimation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Motif</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr" s="1">
+      <c r="L1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Commentaire</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr" s="1">
+      <c r="M1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Statut</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr" s="1">
+      <c r="N1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Cree par</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr" s="1">
+      <c r="O1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Cree le</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr" s="1">
+      <c r="P1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Annule par</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr" s="1">
+      <c r="Q1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Annule le</t>
         </is>
@@ -919,11 +1033,12 @@
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
     <col min="8" max="8" width="14" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -939,35 +1054,40 @@
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Vue</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Semaine</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr" s="1">
+      <c r="E1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Plateforme</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr" s="1">
+      <c r="F1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Code produit</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr" s="1">
+      <c r="G1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Mouvement</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr" s="1">
+      <c r="H1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Quantite</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
+      <c r="I1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Origine</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr" s="1">
+      <c r="J1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Alerte</t>
         </is>
@@ -1052,60 +1172,102 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="17" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">ID alerte</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Date</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Code alerte</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Cle</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Valeur</t>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="10" max="10" width="15" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="26" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID rupture</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Code produit</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Entite</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Plateforme</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Semaine debut</t>
         </is>
       </c>
       <c r="F1" t="inlineStr" s="1">
         <is>
-          <t xml:space="preserve">Seuil</t>
+          <t xml:space="preserve">Semaine fin</t>
         </is>
       </c>
       <c r="G1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Origine</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Cause</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Traitement ventes</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Taux report</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Semaine retour</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Code produit substitut</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Statut</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Acquittee par</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Acquittee le</t>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Commentaire</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Cree par</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Cree le</t>
         </is>
       </c>
     </row>

--- a/modeles/xlsx/SORTIE_SOP.xlsx
+++ b/modeles/xlsx/SORTIE_SOP.xlsx
@@ -12,13 +12,16 @@
     <sheet name="STOCKS_PROJETES" sheetId="8" r:id="rId8"/>
     <sheet name="FIABILITE" sheetId="9" r:id="rId9"/>
     <sheet name="RUPTURES" sheetId="10" r:id="rId10"/>
-    <sheet name="ALERTES" sheetId="11" r:id="rId11"/>
-    <sheet name="DECISIONS" sheetId="12" r:id="rId12"/>
-    <sheet name="JOURNAL" sheetId="13" r:id="rId13"/>
-    <sheet name="OPERATIONS" sheetId="14" r:id="rId14"/>
-    <sheet name="CONTRAT" sheetId="15" r:id="rId15"/>
-    <sheet name="PUBLICATION_MENSUELLE" sheetId="16" r:id="rId16"/>
-    <sheet name="PUBLICATION_HEBDO" sheetId="17" r:id="rId17"/>
+    <sheet name="PLAN_APPRO" sheetId="11" r:id="rId11"/>
+    <sheet name="OCCUPATION_PROJETEE" sheetId="12" r:id="rId12"/>
+    <sheet name="ALERTES" sheetId="13" r:id="rId13"/>
+    <sheet name="DECISIONS" sheetId="14" r:id="rId14"/>
+    <sheet name="JOURNAL" sheetId="15" r:id="rId15"/>
+    <sheet name="OPERATIONS" sheetId="16" r:id="rId16"/>
+    <sheet name="CONTRAT" sheetId="17" r:id="rId17"/>
+    <sheet name="PUBLICATION_MENSUELLE" sheetId="18" r:id="rId18"/>
+    <sheet name="PUBLICATION_APPRO" sheetId="19" r:id="rId19"/>
+    <sheet name="PUBLICATION_HEBDO" sheetId="20" r:id="rId20"/>
   </sheets>
 </workbook>
 </file>
@@ -231,6 +234,208 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="21" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="21" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="26" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID ligne appro</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID version</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Scenario</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Plateforme</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Code produit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Code fournisseur</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Semaine besoin</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Semaine commande</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Semaine livraison</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Quantite besoin brut</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Quantite proposee</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Unite stock</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Contraintes appliquees</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Ecart semaines</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Statut</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Valide par</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Valide le</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Commentaire</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="17" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="17" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID version</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Scenario</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Semaine</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Plateforme</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Niveau</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Cle niveau</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Type capacite</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Unite</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Charge</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Capacite</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Taux pourcent</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Alerte</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
@@ -293,7 +498,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -346,7 +551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -405,7 +610,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -446,7 +651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -487,7 +692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -582,7 +787,191 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="15" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="21" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID campagne</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Version contrat</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID version</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Scenario</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Date validation</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Plateforme</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Code produit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Code fournisseur</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Semaine commande</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Semaine livraison</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Quantite</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Unite stock</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Tonnes</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Statut</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID version</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID campagne</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Numero</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Scenario</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Libelle</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Statut</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Date reunion S&amp;OP</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Version coefficients</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Cree par</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Cree le</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Verrouillee</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Commentaire</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -670,95 +1059,6 @@
       <c r="N1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Tonnes reelle</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">ID version</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">ID campagne</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Numero</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Scenario</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Libelle</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Statut</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Date reunion S&amp;OP</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Version coefficients</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Cree par</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Cree le</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Verrouillee</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commentaire</t>
         </is>
       </c>
     </row>

--- a/modeles/xlsx/SORTIE_SOP.xlsx
+++ b/modeles/xlsx/SORTIE_SOP.xlsx
@@ -13,15 +13,16 @@
     <sheet name="FIABILITE" sheetId="9" r:id="rId9"/>
     <sheet name="RUPTURES" sheetId="10" r:id="rId10"/>
     <sheet name="PLAN_APPRO" sheetId="11" r:id="rId11"/>
-    <sheet name="OCCUPATION_PROJETEE" sheetId="12" r:id="rId12"/>
-    <sheet name="ALERTES" sheetId="13" r:id="rId13"/>
-    <sheet name="DECISIONS" sheetId="14" r:id="rId14"/>
-    <sheet name="JOURNAL" sheetId="15" r:id="rId15"/>
-    <sheet name="OPERATIONS" sheetId="16" r:id="rId16"/>
-    <sheet name="CONTRAT" sheetId="17" r:id="rId17"/>
-    <sheet name="PUBLICATION_MENSUELLE" sheetId="18" r:id="rId18"/>
-    <sheet name="PUBLICATION_APPRO" sheetId="19" r:id="rId19"/>
-    <sheet name="PUBLICATION_HEBDO" sheetId="20" r:id="rId20"/>
+    <sheet name="DEMANDES_DECALAGE" sheetId="12" r:id="rId12"/>
+    <sheet name="OCCUPATION_PROJETEE" sheetId="13" r:id="rId13"/>
+    <sheet name="ALERTES" sheetId="14" r:id="rId14"/>
+    <sheet name="DECISIONS" sheetId="15" r:id="rId15"/>
+    <sheet name="JOURNAL" sheetId="16" r:id="rId16"/>
+    <sheet name="OPERATIONS" sheetId="17" r:id="rId17"/>
+    <sheet name="CONTRAT" sheetId="18" r:id="rId18"/>
+    <sheet name="PUBLICATION_MENSUELLE" sheetId="19" r:id="rId19"/>
+    <sheet name="PUBLICATION_APPRO" sheetId="20" r:id="rId20"/>
+    <sheet name="PUBLICATION_HEBDO" sheetId="21" r:id="rId21"/>
   </sheets>
 </workbook>
 </file>
@@ -248,10 +249,12 @@
     <col min="12" max="12" width="15" customWidth="1"/>
     <col min="13" max="13" width="26" customWidth="1"/>
     <col min="14" max="14" width="18" customWidth="1"/>
-    <col min="15" max="15" width="14" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
+    <col min="15" max="15" width="20" customWidth="1"/>
+    <col min="16" max="16" width="15" customWidth="1"/>
     <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="15" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="20" max="20" width="15" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -327,20 +330,30 @@
       </c>
       <c r="O1" t="inlineStr" s="1">
         <is>
+          <t xml:space="preserve">Origine decalage</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Verrouillee</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr" s="1">
+        <is>
           <t xml:space="preserve">Statut</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr" s="1">
+      <c r="R1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Valide par</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr" s="1">
+      <c r="S1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Valide le</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr" s="1">
+      <c r="T1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Commentaire</t>
         </is>
@@ -351,6 +364,101 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="31" customWidth="1"/>
+    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID demande</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID ligne appro</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Plateforme</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Code produit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Origine</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Demandeur</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Demande le</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Semaine livraison souhaitee</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Date imposee</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Motif</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Decision</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Decide par</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Decide le</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Commentaire</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -433,7 +541,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -498,7 +606,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -551,7 +659,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -610,7 +718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -651,7 +759,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -692,7 +800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -787,7 +895,96 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="24" customWidth="1"/>
+    <col min="10" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
+    <col min="12" max="12" width="15" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID version</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">ID campagne</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Numero</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Type</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Scenario</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Libelle</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Statut</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Date reunion S&amp;OP</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Version coefficients</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Cree par</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Cree le</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Verrouillee</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Commentaire</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -882,96 +1079,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="24" customWidth="1"/>
-    <col min="10" max="10" width="14" customWidth="1"/>
-    <col min="11" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="15" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">ID version</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">ID campagne</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Numero</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Type</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Scenario</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Libelle</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Statut</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Date reunion S&amp;OP</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Version coefficients</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Cree par</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Cree le</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Verrouillee</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr" s="1">
-        <is>
-          <t xml:space="preserve">Commentaire</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>

--- a/modeles/xlsx/SORTIE_SOP.xlsx
+++ b/modeles/xlsx/SORTIE_SOP.xlsx
@@ -93,7 +93,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modèle de structure v0.1 – vide, à compléter</t>
+          <t xml:space="preserve">Modèle de structure v0.7 – à compléter. L'application contrôle que les onglets et colonnes correspondent à cette version.</t>
         </is>
       </c>
     </row>

--- a/modeles/xlsx/SORTIE_SOP.xlsx
+++ b/modeles/xlsx/SORTIE_SOP.xlsx
@@ -93,7 +93,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modèle de structure v0.7 – à compléter. L'application contrôle que les onglets et colonnes correspondent à cette version.</t>
+          <t xml:space="preserve">Modèle de structure v0.8 – à compléter. L'application contrôle que les onglets et colonnes correspondent à cette version.</t>
         </is>
       </c>
     </row>

--- a/modeles/xlsx/SORTIE_SOP.xlsx
+++ b/modeles/xlsx/SORTIE_SOP.xlsx
@@ -93,7 +93,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Modèle de structure v0.8 – à compléter. L'application contrôle que les onglets et colonnes correspondent à cette version.</t>
+          <t xml:space="preserve">Modèle de structure v0.9 – à compléter. L'application contrôle que les onglets et colonnes correspondent à cette version.</t>
         </is>
       </c>
     </row>
@@ -1197,6 +1197,7 @@
     <col min="18" max="18" width="24" customWidth="1"/>
     <col min="19" max="19" width="15" customWidth="1"/>
     <col min="20" max="20" width="14" customWidth="1"/>
+    <col min="21" max="21" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1298,6 +1299,11 @@
       <c r="T1" t="inlineStr" s="1">
         <is>
           <t xml:space="preserve">Modifie le</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr" s="1">
+        <is>
+          <t xml:space="preserve">Qte substitution</t>
         </is>
       </c>
     </row>
